--- a/InputData/trans/BPHEVSP/BAU PHEV Subsidy Perc.xlsx
+++ b/InputData/trans/BPHEVSP/BAU PHEV Subsidy Perc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\State Models\eps-maryland\InputData\trans\BPHEVSP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB16102-7587-4B66-83E2-6259F6B4BD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E8B308-156C-411F-93F0-70BADAD487E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59835" yWindow="2175" windowWidth="24480" windowHeight="13800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60450" yWindow="1710" windowWidth="21825" windowHeight="15060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -865,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="70.81640625" style="3" customWidth="1"/>
@@ -1002,6 +1002,12 @@
         <v>0.88711067149387013</v>
       </c>
       <c r="G33" s="9"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B35" s="3">
+        <f>3000*B33</f>
+        <v>2661.3320144816103</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1617,25 +1623,28 @@
         <v>53</v>
       </c>
       <c r="D21" s="17">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="E21" s="17">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="G21" s="17">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="H21" s="17">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I21" s="17">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="J21" s="17">
-        <v>2500</v>
+        <v>3000</v>
+      </c>
+      <c r="K21" s="17">
+        <v>3000</v>
       </c>
     </row>
     <row r="22" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1930,123 +1939,127 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C33" s="2">
+        <f t="shared" ref="C33" si="1">SUMPRODUCT(D13:D26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="D33" s="2">
+        <f t="shared" ref="D33" si="2">SUMPRODUCT(E13:E26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="E33" s="2">
+        <f t="shared" ref="E33" si="3">SUMPRODUCT(F13:F26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="F33" s="2">
-        <f t="shared" ref="D33:I33" si="1">SUMPRODUCT(G13:G26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
-        <v>2500</v>
+        <f t="shared" ref="F33:I33" si="4">SUMPRODUCT(G13:G26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
+        <v>3000</v>
       </c>
       <c r="G33" s="2">
-        <f t="shared" si="1"/>
-        <v>2500</v>
+        <f t="shared" ref="G33" si="5">SUMPRODUCT(H13:H26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
+        <v>3000</v>
       </c>
       <c r="H33" s="2">
-        <f t="shared" si="1"/>
-        <v>2500</v>
+        <f t="shared" ref="H33" si="6">SUMPRODUCT(I13:I26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
+        <v>3000</v>
       </c>
       <c r="I33" s="2">
-        <f t="shared" si="1"/>
-        <v>2500</v>
+        <f t="shared" ref="I33" si="7">SUMPRODUCT(J13:J26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
+        <v>3000</v>
       </c>
       <c r="J33" s="2">
-        <f>I33</f>
-        <v>2500</v>
+        <f t="shared" ref="J33" si="8">SUMPRODUCT(K13:K26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
+        <v>3000</v>
       </c>
       <c r="K33" s="2">
+        <f t="shared" ref="K33" si="9">SUMPRODUCT(L13:L26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="L33" s="2">
-        <f t="shared" ref="K33:AG33" si="2">K33</f>
+        <f t="shared" ref="L33" si="10">SUMPRODUCT(M13:M26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="M33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="M33" si="11">SUMPRODUCT(N13:N26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="N33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="N33" si="12">SUMPRODUCT(O13:O26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="O33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="O33" si="13">SUMPRODUCT(P13:P26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="P33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="P33" si="14">SUMPRODUCT(Q13:Q26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="Q33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="Q33" si="15">SUMPRODUCT(R13:R26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="R33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="R33" si="16">SUMPRODUCT(S13:S26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="S33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="S33" si="17">SUMPRODUCT(T13:T26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="T33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="T33" si="18">SUMPRODUCT(U13:U26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="U33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="U33" si="19">SUMPRODUCT(V13:V26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="V33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="V33" si="20">SUMPRODUCT(W13:W26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="W33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="W33" si="21">SUMPRODUCT(X13:X26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="X33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="X33" si="22">SUMPRODUCT(Y13:Y26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="Y33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="Y33" si="23">SUMPRODUCT(Z13:Z26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="Z33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="Z33" si="24">SUMPRODUCT(AA13:AA26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="AA33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AA33" si="25">SUMPRODUCT(AB13:AB26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="AB33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AB33" si="26">SUMPRODUCT(AC13:AC26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="AC33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AC33" si="27">SUMPRODUCT(AD13:AD26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="AD33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AD33" si="28">SUMPRODUCT(AE13:AE26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="AE33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AE33" si="29">SUMPRODUCT(AF13:AF26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="AF33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AF33" si="30">SUMPRODUCT(AG13:AG26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
       <c r="AG33" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AG33" si="31">SUMPRODUCT(AH13:AH26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>0</v>
       </c>
     </row>
@@ -2205,23 +2218,23 @@
       </c>
       <c r="F38" s="2">
         <f>(D3+F33)*About!$B$33</f>
-        <v>3640.6387761629412</v>
+        <v>4084.1941119098765</v>
       </c>
       <c r="G38" s="2">
         <f>(E3+G33)*About!$B$33</f>
-        <v>3056.2413080314896</v>
+        <v>3499.7966437784248</v>
       </c>
       <c r="H38" s="2">
         <f>(F3+H33)*About!$B$33</f>
-        <v>2638.8650500230365</v>
+        <v>3082.4203857699713</v>
       </c>
       <c r="I38" s="2">
         <f>(G3+I33)*About!$B$33</f>
-        <v>2518.3001970864234</v>
+        <v>2961.8555328333582</v>
       </c>
       <c r="J38" s="2">
         <f>(H3+J33)*About!$B$33</f>
-        <v>2518.3001970864234</v>
+        <v>2961.8555328333582</v>
       </c>
       <c r="K38" s="2">
         <f>(I3+K33)*About!$B$33</f>
@@ -2620,123 +2633,123 @@
         <v>0.18016388732564667</v>
       </c>
       <c r="D45" s="7">
-        <f t="shared" ref="D45:AG45" si="3">D38/C41</f>
+        <f t="shared" ref="D45:AG45" si="32">D38/C41</f>
         <v>0.1781803175643257</v>
       </c>
       <c r="E45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>9.6896533338125937E-2</v>
       </c>
       <c r="F45" s="7">
-        <f t="shared" si="3"/>
-        <v>9.7075934622908602E-2</v>
+        <f t="shared" si="32"/>
+        <v>0.10890313073380467</v>
       </c>
       <c r="G45" s="7">
-        <f t="shared" si="3"/>
-        <v>8.1456324840924563E-2</v>
+        <f t="shared" si="32"/>
+        <v>9.32781621476126E-2</v>
       </c>
       <c r="H45" s="7">
-        <f t="shared" si="3"/>
-        <v>7.011917548023161E-2</v>
+        <f t="shared" si="32"/>
+        <v>8.1905202364084898E-2</v>
       </c>
       <c r="I45" s="7">
-        <f t="shared" si="3"/>
-        <v>6.6848062143937764E-2</v>
+        <f t="shared" si="32"/>
+        <v>7.8622200383132251E-2</v>
       </c>
       <c r="J45" s="7">
-        <f t="shared" si="3"/>
-        <v>6.6803729662477745E-2</v>
+        <f t="shared" si="32"/>
+        <v>7.857005949633547E-2</v>
       </c>
       <c r="K45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.9634193214199959E-3</v>
       </c>
       <c r="L45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.9516197902245803E-3</v>
       </c>
       <c r="M45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.9377580124603223E-3</v>
       </c>
       <c r="N45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.9224822279215408E-3</v>
       </c>
       <c r="O45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>6.4493098638198163E-3</v>
       </c>
       <c r="P45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>3.9230098371081726E-3</v>
       </c>
       <c r="Q45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>1.5268255803143347E-3</v>
       </c>
       <c r="R45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>3.042440593046421E-4</v>
       </c>
       <c r="S45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.7969311125697645E-5</v>
       </c>
       <c r="T45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.7924474237160522E-5</v>
       </c>
       <c r="U45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.7904110875978027E-5</v>
       </c>
       <c r="V45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.7889862854445594E-5</v>
       </c>
       <c r="W45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.7900039480808213E-5</v>
       </c>
       <c r="X45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.790003948080824E-5</v>
       </c>
       <c r="Y45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.7910218766753334E-5</v>
       </c>
       <c r="Z45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.7934659910358932E-5</v>
       </c>
       <c r="AA45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.7959116393594405E-5</v>
       </c>
       <c r="AB45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.7983588230905353E-5</v>
       </c>
       <c r="AC45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.8012158132910721E-5</v>
       </c>
       <c r="AD45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.8032578025626903E-5</v>
       </c>
       <c r="AE45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>7.8050965071110089E-5</v>
       </c>
       <c r="AF45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>2.9274477036873986E-5</v>
       </c>
       <c r="AG45" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -18730,23 +18743,23 @@
       </c>
       <c r="E2" s="9">
         <f>Summary!F38</f>
-        <v>3640.6387761629412</v>
+        <v>4084.1941119098765</v>
       </c>
       <c r="F2" s="9">
         <f>Summary!G38</f>
-        <v>3056.2413080314896</v>
+        <v>3499.7966437784248</v>
       </c>
       <c r="G2" s="9">
         <f>Summary!H38</f>
-        <v>2638.8650500230365</v>
+        <v>3082.4203857699713</v>
       </c>
       <c r="H2" s="9">
         <f>Summary!I38</f>
-        <v>2518.3001970864234</v>
+        <v>2961.8555328333582</v>
       </c>
       <c r="I2" s="9">
         <f>Summary!J38</f>
-        <v>2518.3001970864234</v>
+        <v>2961.8555328333582</v>
       </c>
       <c r="J2" s="9">
         <f>Summary!K38</f>

--- a/InputData/trans/BPHEVSP/BAU PHEV Subsidy Perc.xlsx
+++ b/InputData/trans/BPHEVSP/BAU PHEV Subsidy Perc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\State Models\eps-maryland\InputData\trans\BPHEVSP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E8B308-156C-411F-93F0-70BADAD487E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CCECC19-F608-4088-AF41-4D50B5778E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60450" yWindow="1710" windowWidth="21825" windowHeight="15060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="58770" yWindow="2100" windowWidth="23100" windowHeight="13305" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="2">
-        <f t="shared" ref="F33:I33" si="4">SUMPRODUCT(G13:G26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
+        <f t="shared" ref="F33" si="4">SUMPRODUCT(G13:G26,$B$13:$B$26)/SUM($B$13:$B$26)</f>
         <v>3000</v>
       </c>
       <c r="G33" s="2">
